--- a/data_extactor/batch_10_fa/trimmed/batch_0081_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0081_fa_trim.xlsx
@@ -503,22 +503,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت سفارش کار | نرم‌افزار مسیریابی | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | Microsoft Windows | نرم‌افزار مرورگر وب</t>
+          <t>Facebook | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار مرورگر وب | نرم‌افزار دستور کار</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | ساختمان و سازه | مهندسی و فناوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | دید نزدیک | حساسیت به مسئله | استحکام تنه | چابکی انگشتان | هماهنگی چندعضوی</t>
+          <t>مهارت دستی | ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | قدرت تنه | مهارت انگشتان | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نجاران | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | برق‌کاران | نصابان و تعمیرکاران آسانسور و پله‌برقی | نصابان فنس و نرده | قفل‌سازان و تعمیرکاران گاوصندوق | کارگران عمومی تعمیرات و نگهداری</t>
+          <t>نجاران و درودگران | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | برق‌کاران | نصابان و تعمیرکاران آسانسور و پله‌برقی | نصابان فنس و حصار | قفل‌سازان و تعمیرکاران گاوصندوق | کارگران عمومی تعمیرات و نگهداری تاسیسات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال | نگارش | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات</t>
+          <t>مکانیک | مهندسی و فناوری | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید نزدیک | ثبات دست و بازو | مرتب‌سازی اطلاعات | استدلال قیاسی | چابکی دستی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت دستی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات تجاری و صنعتی | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | مکانیک‌های ماشین‌آلات صنعتی | لوله‌کش‌ها و نصابان لوله‌های آب و بخار</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | مکانیک‌های ماشین‌آلات صنعتی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و سازه | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | رایانه و الکترونیک | ایمنی و امنیت عمومی | فیزیک</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مهندسی و فناوری | رایانه و الکترونیک | ایمنی و امنیت عمومی | فیزیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | استدلال قیاسی | درک شفاهی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | درک شفاهی | ثبات دست و بازو | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دیگ‌سازان صنعتی | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله‌های بخار | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | لوله‌کش‌ها و نصابان لوله‌های آب و بخار | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک | مدیریت و امور اداری | رایانه و الکترونیک | فروش و بازاریابی | مهندسی و فناوری</t>
+          <t>خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | رایانه و الکترونیک | فروش و بازاریابی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | حساسیت به مسئله | چابکی دستی | چابکی انگشتان | دید نزدیک | بیان شفاهی | تجسم فضایی</t>
+          <t>ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | مهارت انگشتان | بینایی نزدیک | بیان شفاهی | تجسم</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران عمومی تعمیرات و نگهداری | مکانیک‌های ماشین‌آلات و تجهیزات موتوری کوچک</t>
+          <t>نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران عمومی تعمیرات و نگهداری تاسیسات | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | یادگیری فعال | نظارت | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | تولید و پردازش | مهندسی و فناوری | طراحی | ریاضیات | رایانه و الکترونیک</t>
+          <t>مکانیک | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | طراحی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | چابکی دستی | چابکی انگشتان | دقت کنترل | دید نزدیک | ثبات دست و بازو | هماهنگی چندعضوی</t>
+          <t>حساسیت به مسئله | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | ثبات دست و بازو | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین (میل‌رایت) | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره فلز و پلاستیک</t>
+          <t>نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و پردازش | مدیریت و امور اداری | زبان انگلیسی | طراحی</t>
+          <t>مکانیک | تولید و فرآوری | مدیریت و اداره | زبان انگلیسی | طراحی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | حساسیت به مسئله | دید نزدیک | چابکی دستی | دقت کنترل | انعطاف‌پذیری بدنی | هماهنگی چندعضوی</t>
+          <t>ثبات دست و بازو | حساسیت به مسئله | بینایی نزدیک | مهارت دستی | دقت کنترل | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | کارگران کمکی نصابان، تعمیرکاران و عوامل نگهداری | مکانیک‌های ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | تعمیرکاران واگن‌های قطار</t>
+          <t>نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران کمکی نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | مکانیک تجهیزات سنگین متحرک | تعمیرکار واگن قطار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dassault Systemes SolidWorks | Autodesk AutoCAD | SAP | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+          <t>Dassault Systemes SolidWorks | Autodesk AutoCAD | SAP | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | ساختمان و سازه | مهندسی و فناوری | ایمنی و امنیت عمومی | طراحی | تولید و پردازش</t>
+          <t>مکانیک | ریاضیات | ساختمان و ساخت‌وساز | مهندسی و فناوری | ایمنی و امنیت عمومی | طراحی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | دقت کنترل | هماهنگی چندعضوی</t>
+          <t>مهارت دستی | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دیگ‌سازان صنعتی | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | ریگرها و باربندهای تجهیزات سنگین</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت نگهداری و تعمیرات | نرم‌افزار ثبت ساعت کارکرد و حضور و غیاب | Microsoft Access | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+          <t>نرم‌افزار مدیریت تعمیر و نگهداری | نرم‌افزار ثبت ساعت کارکرد و حضور و غیاب | Microsoft Access | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | انعطاف‌پذیری بدنی | هماهنگی چندعضوی | دقت کنترل | چابکی دستی | استحکام تنه</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | دقت کنترل | مهارت دستی | قدرت تنه</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>دیگ‌سازان صنعتی | بناهای آجر و بلوک | بتن‌ریزان و پرداخت‌کاران بتن | کارگران کمکی بنایان آجر، بلوک، سنگ و کاشی‌کاران | عایق‌کاران کف، سقف و دیوار | اپراتورها و مراقبان کوره‌های تصفیه و ذوب فلز | مذاب‌ریزان و ریخته‌گران فلزات</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | بنایان و سفت‌کاران ساختمان | بتن‌ریزان و پرداخت‌کاران بتن | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | ریخته‌گران و متصدیان بارریزی مذاب فلزات</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی | حمل‌ونقل | مکانیک | خدمات مشتریان و خدمات فردی</t>
+          <t>ساختمان و ساخت‌وساز | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | حمل و نقل | مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چندعضوی | دید نزدیک | دقت کنترل | چابکی دستی | تعادل کلی بدن</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | بینایی نزدیک | دقت کنترل | مهارت دستی | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | تعمیرکاران تجهیزات الکتریکی نیروگاه‌ها، پست‌ها و رله‌ها | برق‌کاران | کارگران کمکی برق‌کاران | اپراتورهای بالابر و وینچ | دیسپاچرها و توزیع‌کنندگان انرژی الکتریکی | نصابان و کابل‌کشان خطوط مخابراتی</t>
+          <t>تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | برق‌کاران | کمک‌برق‌کاران | اپراتورهای بالابر و وینچ | دیسپچرها و توزیع‌کنندگان شبکه برق | نصابان و کابل‌کشان خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | نظارت | شنیدن فعال</t>
+          <t>سخن گفتن | تفکر انتقادی | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مخابرات | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مکانیک | ارتباطات و رسانه</t>
+          <t>مخابرات | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مکانیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | انعطاف‌پذیری بدنی | ثبات دست و بازو | حساسیت به مسئله | چابکی دستی | هماهنگی چندعضوی</t>
+          <t>درک شفاهی | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | برق‌کاران | نصابان و تعمیرکاران تجهیزات رادیویی، دکل‌ها و سایت‌های سلولار | نصابان سیستم‌های دزدگیر، امنیتی و اعلام حریق | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | برق‌کاران | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | نصاب سیستم‌های اعلام سرقت و حریق | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
